--- a/event_registration_forms/009_whiskey_enthusiasts_club_membership_form--event_registration_forms.xlsx
+++ b/event_registration_forms/009_whiskey_enthusiasts_club_membership_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'annual'}</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Annual'}</t>
+          <t>Annual</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'lifetime'}</t>
+          <t>lifetime</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Lifetime'}</t>
+          <t>Lifetime</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'fruity'}</t>
+          <t>fruity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Fruity'}</t>
+          <t>Fruity</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'spicy'}</t>
+          <t>spicy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Spicy'}</t>
+          <t>Spicy</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'floral'}</t>
+          <t>floral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Floral'}</t>
+          <t>Floral</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'vanilla'}</t>
+          <t>vanilla</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Vanilla'}</t>
+          <t>Vanilla</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'woody'}</t>
+          <t>woody</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Woody'}</t>
+          <t>Woody</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'regular_newsletter'}</t>
+          <t>regular_newsletter</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Regular Newsletter'}</t>
+          <t>Regular Newsletter</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'special_offers'}</t>
+          <t>special_offers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Special Offers'}</t>
+          <t>Special Offers</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'early_access'}</t>
+          <t>early_access</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Early Access'}</t>
+          <t>Early Access</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'all_of_the_above'}</t>
+          <t>all_of_the_above</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'All of the above'}</t>
+          <t>All of the above</t>
         </is>
       </c>
     </row>
